--- a/Влад_контакты_Сколковская_миля.xlsx
+++ b/Влад_контакты_Сколковская_миля.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Влад — все контакты" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шаблоны сообщений" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Влад — все контакты'!$A$1:$S$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +36,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="001F4E79"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -43,7 +49,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF3FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,21 +93,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -467,25 +484,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P76"/>
+  <dimension ref="A1:S76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="35" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
     <col width="32" customWidth="1" min="10" max="10"/>
     <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="60" customWidth="1" min="15" max="15"/>
-    <col width="80" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="65" customWidth="1" min="16" max="16"/>
+    <col width="65" customWidth="1" min="17" max="17"/>
+    <col width="65" customWidth="1" min="18" max="18"/>
+    <col width="85" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,30 +561,45 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TenChat</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Ответственный</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Сообщение TG/VK — вар. 1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Сообщение TG/VK — вар. 2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Сообщение TG/VK — вар. 3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Письмо Email</t>
         </is>
@@ -611,49 +646,52 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>https://altekproekt.ru</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Дмитрий, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Дмитрий, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Дмитрий, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Дмитрий, привет! Скажи, директор и учредитель ООО «АЛЬТЕК СТРОЙ ПРОЕКТ» в ... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Дмитрий, привет! Скажи, директор и учредитель ООО «АЛЬТЕК СТРОЙ ПРОЕКТ» в Екатеринбу… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Дмитрий, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -661,89 +699,92 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Коваленко Светлана</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Заместитель директора «Эксперт-Урал»</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Заместитель директора «Эксперт-Урал» (деловое СМИ об экономике Урала)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>СМИ, маркетинг, реклама, BTL, PR, дизайн, продюсирование</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>+7 (343) 345-03-42</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>expertural@expertural.com</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>https://expert-ural.com/?ysclid=mmkonpscgj988761590</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Светлана, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Светлана, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Светлана, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Светлана, привет! Скажи, Заместитель директора «Эксперт-Урал» - это сетевое... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Светлана, привет! Скажи, Заместитель директора «Эксперт-Урал» - это сетевое издание, … участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Светлана, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -771,7 +812,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Основатель и дизайнер бренда ЯRMYSHEVA</t>
+          <t>Основатель и дизайнер бренда ЯRMYSHEVA (одежда, шоу-рум Екатеринбург)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -787,49 +828,56 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>https://instagram.com/yarmyshevamariya</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>https://yarmysheva.ru</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Мария, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Мария, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Мария, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Мария, привет! Скажи, ЯRMYSHEVA – интернет-магазин эксклюзивной дизайнер... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Мария, привет! Скажи, ЯRMYSHEVA – интернет-магазин эксклюзивной дизайнерской одежд… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Мария, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -837,77 +885,84 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Сунин Максим</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Был ген диром компании Willsun («Торговля оптовая лесоматериалами, строительными материалами и санитарно-техническим оборудованием»)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Бывший ген.дир Willsun (компания ликвидирована)</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Бывший ген.дир Willsun (ликвидирована). Выпускник Сколково</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Металлургия, металлообработка</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/%D0%BC%D0%B0%D0%BA%D1%81%D0%B8%D0%BC-%D1%81%D1%83%D0%BD%D0%B8%D0%BD-01198992</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Максим, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Максим, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Максим, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Максим, привет! Скажи, Ликвидирована участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>Максим, привет! Скажи, Ликвидирована участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Максим, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -935,7 +990,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Адвокат, депутат Екатеринбургской гордумы, основатель Волонтёрского центра</t>
+          <t>Адвокат, депутат Екатеринбургской гордумы, основатель Волонтёрского центра. TG-канал: @viharevofficial</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -945,10 +1000,14 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>+7 (922) 130-44-33</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>+7 (912) 207-19-54</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/aviharev</t>
+        </is>
+      </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
           <t>aviharev-vc@yandex.ru</t>
@@ -956,52 +1015,55 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>https://vk.com/volunteersekb</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+          <t>https://vk.com/aleksey_vikharev</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>https://vk.com/volunteersekb?ysclid=mmks6mbjwn20400603</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Алексей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Алексей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>Алексей, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Мероприятие проводится совместно со Сколково — открыты к партнёрству с организациями, которые развивают социальные и инвестиционные проекты.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Алексей, привет! Скажи, Основатель Волонтерского центра - Алексей Андрееви... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Алексей, привет! Скажи, Основатель Волонтерского центра - Алексей Андреевич Вихарев.… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Алексей, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -1009,82 +1071,89 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Рутковский Евгений</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Директор и учредитель ООО «КВАРТА»</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Директор и учредитель ООО «КВАРТА» (грузоперевозки, спецтехника)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Перевозки, логистика, склад, ВЭД</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>+7 (343) 226-02-72</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/evgeniy-rutkovskiy-7756a6b8</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Евгений, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>Евгений, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Евгений, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Событие объединяет любителей бега и предпринимателей Сколково — отличная точка для тех, кто близок к спорту и социальным проектам.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>Евгений, привет! Скажи, Учредитель и директор ООО «КВАРТА»: 
-деятельность ... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
+деятельность автомобиль… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Евгений, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -1112,7 +1181,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Основатель и владелец сети магазинов «Жизньмарт»</t>
+          <t>Основатель «Жизньмарт», «Сушкоф», «Дель Песто» — сети кулинарии и ресторанов</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1127,50 +1196,61 @@
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>https://vk.com/id168352990</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>https://tenchat.ru/izaychenko</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>https://zhiznmart.ru</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Иван, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Иван, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>Иван, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Иван, привет! Скажи, Основатель и владелец «Жизньмарт» — российская сет... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
+Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Иван, привет! Скажи, Основатель и владелец «Жизньмарт» — российская сеть магазино… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Иван, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -1178,85 +1258,92 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Ларин Дмитрий</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Директор по трейд-маркетингу Okkam</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Директор по трейд-маркетингу Okkam (коммуникационная группа полного цикла)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Информационные технологии, телекоммуникации</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Dmitry.Larin@okkam.ru</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dmitriy-larin-b52755a0</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>https://okkam.group/team/dmitrij_larin?ysclid=mmksvz2uw77642129</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Дмитрий, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Дмитрий, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Дмитрий, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Дмитрий, привет! Скажи, ??? директора по трейд-маркетингу в компании Okkam... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
+Партнёрство даёт выход на топ-менеджеров крупнейшей деловой сети Сколково.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>Дмитрий, привет! Скажи, ??? директора по трейд-маркетингу в компании Okkam - коммуни… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Дмитрий, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Партнёрство даёт выход на топ-менеджеров крупнейшей деловой сети Сколково.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -1284,7 +1371,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Бывший сотрудник Бергауф / Isover (строительные материалы)</t>
+          <t>Бывший сотрудник Бергауф / Isover (строительные материалы, Saint-Gobain)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1297,44 +1384,47 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Ирина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Ирина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>Ирина, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Ирина, привет! Скажи, В 2017 году она перешла в Isover из компании «Берг... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Ирина, привет! Скажи, В 2017 году она перешла в Isover из компании «Бергауф Строит… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Ирина, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -1342,85 +1432,100 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Кузовков Василий</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Директор ООО ИК «Энергософт»</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Директор ООО ИК «Энергософт» (инжиниринг в электроэнергетике, выручка 866 млн ₽)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Энергетика</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>7 929 220 0307</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/vasiliykuz</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>len-nik2004@bk.ru</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>https://tenchat.ru/0418785</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>https://энергософт.рф</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Василий, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>Василий, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Василий, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Василий, привет! Скажи, директор ООО ИК «Энергософт»-  динамичная инжинири... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>Василий, привет! Скажи, директор ООО ИК «Энергософт»-  динамичная инжиниринговая ком… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Василий, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -1448,7 +1553,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Ресторатор, основатель сети ресторанов (Екатеринбург)</t>
+          <t>Ресторатор: «Креветки и бургеры», Comunale, Pumpula, Jackie, Морская/10 (Екатеринбург)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1457,48 +1562,59 @@
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/A_Maximow</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>mr@tmr.rest</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Андрей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Андрей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>Андрей, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Андрей, привет! Скажи, екатеринбургский ресторатор, основатель и владелец... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
+Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>Андрей, привет! Скажи, екатеринбургский ресторатор, основатель и владелец сети рест… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Андрей, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -1506,77 +1622,92 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Братцев Иван</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Основатель КФХ Братцева, фермер (Екатеринбург)</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Основатель КФХ Братцева (овцеводство), интернет-магазин «Ванина Баранина»</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Сельское хозяйство</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>+7 (912) 655-08-68</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/i_brattsev</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>https://vaninabaranina.ru</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Иван, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>Иван, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>Иван, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Иван, привет! Скажи, 1) Крестьянское (фермерское) хозяйство Братцева - ... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
+        <is>
+          <t>Иван, привет! Скажи, 1) Крестьянское (фермерское) хозяйство Братцева - разведение… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Иван, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -1604,7 +1735,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Ген.дир ООО «Маритоль» (обслуживание МКД)</t>
+          <t>Ген.дир ООО «Маритоль» (обслуживание и ремонт МКД, выручка 250 млн ₽). WhatsApp: +7 902 871-43-43</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1617,56 +1748,63 @@
           <t>+7 (343) 268-30-61</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/Semen_Snitsar</t>
+        </is>
+      </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
           <t>info@maritol.ru</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>https://maritol.ru/about/</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Семен, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Семен, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>Семен, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Семен, привет! Скажи, директор и единственный учредитель ООО «Маритоль» ... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Семен, привет! Скажи, директор и единственный учредитель ООО «Маритоль» - обслужив… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Семен, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -1674,81 +1812,88 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Донсков Андрей</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Директор ООО «Автопрокат Екб»</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Директор ООО «Автопрокат Екб» (аренда авто, Екатеринбург)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Автомобильный бизнес</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/ADonskov</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>https://autoprocat.ru</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Андрей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>Андрей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>Андрей, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Событие объединяет любителей бега и предпринимателей Сколково — отличная точка для тех, кто близок к спорту и социальным проектам.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Андрей, привет! Скажи, директор и единственный учредитель ООО «Автопрокат... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>Андрей, привет! Скажи, директор и единственный учредитель ООО «Автопрокат Екб»  -  … участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Андрей, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -1776,7 +1921,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>К.психол.н., основатель проекта «МыРядом2020»</t>
+          <t>К.психол.н., основатель проекта «МыРядом2020» (200+ психологов, 25 000+ консультаций)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1789,57 +1934,64 @@
           <t>+7 922 170 07 81</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/Amallianda</t>
+        </is>
+      </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
           <t>2133940@mail.ru</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>https://www.мырядом2020.рф
 https://nadezdasafyan.orgs.biz</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Надежда, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Надежда, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>Надежда, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Надежда, привет! Скажи, Автор двух проектов: «МыРядом2020» оказывает психо... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>Надежда, привет! Скажи, Автор двух проектов: «МыРядом2020» оказывает психологическую… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Надежда, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -1847,77 +1999,88 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Высотский Сергей</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Учредитель ООО «Мастер Трак» (грузоперевозки)</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Учредитель ООО «Мастер Трак» / ГК TETRA TRANS (грузоперевозки, выручка 112 млн ₽)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Перевозки, логистика, склад, ВЭД</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/Sergey_Vysotskiy</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>https://tetratrans.ru</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Сергей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Сергей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Сергей, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Сергей, привет! Скажи, учредитель и управляющиц ООО «Мастер Трак» - компа... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t>Сергей, привет! Скажи, учредитель и управляющиц ООО «Мастер Трак» - компания может … участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Сергей, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -1945,7 +2108,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Директор ООО «Академхолл» / проект СПА-комплекса</t>
+          <t>Директор ООО «Академхолл» (застройщик) + ООО «Бани Космос» (банный комплекс Екатеринбург)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1953,53 +2116,72 @@
           <t>Услуги для населения</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 521-22-02</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/Oksana_Zhuikova</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>upr@bani-ekb.ru</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>https://vk.com/kosmosbani</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>https://kosmosbaniekb.ru/?ysclid=mmktoo9ied38911356</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Оксана, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Оксана, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>Оксана, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Оксана, привет! Скажи, 1) директор и один из учредителей ООО «Академхолл»... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Оксана, привет! Скажи, 1) директор и один из учредителей ООО «Академхолл» - деятель… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Оксана, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -2007,89 +2189,96 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Лунин Станислав</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Основатель «ИТ-Альянс» (IT-интегратор)</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Основатель «ИТ-Альянс» (IT-интегратор, поставки оборудования Минцифры и банкам)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Электроника, приборостроение, бытовая техника, компьютеры и оргтехника</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>+7 (343) 351-08-22</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/stas_lunin</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>it@ita1.ru</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>https://ita1.ru</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Станислав, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>Станислав, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>Станислав, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Станислав, привет! Скажи, 1) основатель компании «ИТ-Альянс» - Изначально би... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr">
+        <is>
+          <t>Станислав, привет! Скажи, 1) основатель компании «ИТ-Альянс» - Изначально бизнес начин… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Станислав, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -2117,7 +2306,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Ген.дир ООО «НПЦ «НовАТранс» (IT/разработка ПО)</t>
+          <t>Ген.дир ООО «НПЦ «НовАТранс» (разработка ПО, выручка 196 млн ₽)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2130,56 +2319,63 @@
           <t>7 902 409 9449</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/Rafail_Valiev</t>
+        </is>
+      </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
           <t>info@npcat.ru</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>https://npcat.ru</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Рафаил, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Рафаил, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>Рафаил, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Рафаил, привет! Скажи, Ген дир ООО "НПЦ "НОВАТРАНС" - Компания занимается... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
+Партнёрство даёт выход на топ-менеджеров крупнейшей деловой сети Сколково.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Рафаил, привет! Скажи, Ген дир ООО "НПЦ "НОВАТРАНС" - Компания занимается разработк… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Рафаил, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Партнёрство даёт выход на топ-менеджеров крупнейшей деловой сети Сколково.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -2187,89 +2383,96 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Еланцева Елена</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Основатель бренда Moveli (премиальные сумки)</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Основатель бренда Moveli (премиальные сумки и аксессуары из натуральной кожи)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Розничная торговля</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>+7 922 209 5898</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/elantseva_helen</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>info@moveli.ru</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>https://www.moveli.ru/page/about-us?ysclid=mmkv8fjfw413881454</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Елена, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>Елена, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>Елена, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Елена, привет! Скажи, основатель бренда Moveli - Moveli создает премиаль... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>Елена, привет! Скажи, основатель бренда Moveli - Moveli создает премиальные сумки … участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Елена, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -2297,7 +2500,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Бывший директор ООО «РП-ГРУПП» (компания ликвидирована)</t>
+          <t>Предприниматель. Прежние компании ликвидированы. Текущая: ООО «ИНФО ГРУПП»</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2310,44 +2513,48 @@
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>Антон, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Антон, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>Антон, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>Антон, привет! Скажи, был директором ООО «РП — ГРУПП». Компания ликвидир... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>Антон, привет! Скажи, был директором ООО «РП — ГРУПП». Компания ликвидирована 
+ООО… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Антон, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -2355,85 +2562,100 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Пятыгин Сергей</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Директор ООО ГПК «ЭЛИТТЕНТ» (тентовые конструкции)</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Директор ООО ГПК «ЭЛИТТЕНТ» (тентовые конструкции для промышленности). Моб: +7 (922) 110-07-33</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Промышленное оборудование, техника, станки и комплектующие</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>+7 (922) 110-07-33</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>+7 (343) 382-80-68</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>info@elittent.org</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>https://vk.com/elittent</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>https://tenchat.ru/0506578</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>https://elittent.org/company/</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>Сергей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>Сергей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>Сергей, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>Сергей, привет! Скажи, директор и учредитель ООО ГПК «ЭЛИТТЕНТ» - которое... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>Сергей, привет! Скажи, директор и учредитель ООО ГПК «ЭЛИТТЕНТ» - которое занимаетс… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Сергей, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -2461,7 +2683,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Руководитель ООО «Новый Вкус» (рестораны)</t>
+          <t>Руководитель ООО «Новый Вкус» / «Рататуй» (рестораны и доставка, Екатеринбург)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2469,7 +2691,11 @@
           <t>HoReCa</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 288-52-88</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -2478,44 +2704,51 @@
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>https://rtt-96.ru</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>Сергей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Сергей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>Сергей, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>Сергей, привет! Скажи, Руководитель ООО «НОВЫЙ ВКУС» - деятельность ресто... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
+Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>Сергей, привет! Скажи, Руководитель ООО «НОВЫЙ ВКУС» - деятельность ресторанов и ус… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Сергей, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -2523,89 +2756,96 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Сизганова Евгения</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Директор ИП, коттеджный посёлок «Сакура Парк»</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Директор ИП, коттеджный посёлок «Сакура Парк» (Екатеринбург)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Отрасль не определена</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>+7 922 609 1668</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/evgenia_sizganova</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>info@zemlya-kyrganovo.ru</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>https://kp96.ru/contacts/</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>Евгения, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>Евгения, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>Евгения, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>Евгения, привет! Скажи, директор коттеджного посёлка «Сакура Парк - участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>Евгения, привет! Скажи, директор коттеджного посёлка «Сакура Парк - участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Евгения, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -2633,7 +2873,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Директор IZI.show (техобеспечение мероприятий)</t>
+          <t>Директор IZI.show (техническое обеспечение мероприятий offline/online)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2646,56 +2886,63 @@
           <t>+7 953 040 4045</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/telizin</t>
+        </is>
+      </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
           <t>izi@izi.show</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>https://izi.show/about/</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>Антон, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Антон, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>Антон, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>Антон, привет! Скажи, директор компании IZI.show - Компания по техническ... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Антон, привет! Скажи, директор компании IZI.show - Компания по техническому обеспе… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Антон, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -2703,77 +2950,84 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Удельнова Ирина</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Руководитель ООО «ИМ Диджитал»</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Руководитель ООО «ИМ Диджитал» / ИП (электромонтаж + диджитал, Екатеринбург)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Строительство, недвижимость, эксплуатация, проектирование</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/IrenaMiu</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>Ирина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>Ирина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>Ирина, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>Ирина, привет! Скажи, ООО «ИМ Диджитал» - занимается производством элект... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R27" s="4" t="inlineStr">
+        <is>
+          <t>Ирина, привет! Скажи, ООО «ИМ Диджитал» - занимается производством электромонтажны… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S27" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Ирина, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -2801,7 +3055,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Владелец ООО «АБЗ Красный» (производство асфальта)</t>
+          <t>Владелец ООО «АБЗ Красный» (асфальт), TheGamix, Altyre (IT/игры, склады). Сайт gareev.com. Доп. email: info@abzred.ru</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2809,53 +3063,72 @@
           <t>Строительство, недвижимость, эксплуатация, проектирование</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>+7 912 222 7887</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/Gareevrr</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>920618@mail.ru</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>https://tenchat.ru/gareevrr</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>https://gareev.com</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>Роман, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Роман, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>Роман, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>Роман, привет! Скажи, Владелец компаний в сфере производства асфальта, р... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>Роман, привет! Скажи, Владелец компаний в сфере производства асфальта, разработки … участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Роман, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -2863,81 +3136,88 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Дерябина (Рыбкина) Татьяна</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>ИП Дерябина Татьяна Евгеньевна (флористика)</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>ИП Дерябина Татьяна Евгеньевна (флористика, розничная торговля цветами, Екатеринбург)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Розничная торговля</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>7 929 220 0197</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/deryabinats</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>(Рыбкина), привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>(Рыбкина), привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>(Рыбкина), добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>(Рыбкина), привет! Скажи, ИП Дерябина Татьяна Евгеньевна - Торговля рознична... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R29" s="4" t="inlineStr">
+        <is>
+          <t>(Рыбкина), привет! Скажи, ИП Дерябина Татьяна Евгеньевна - Торговля розничная цветами … участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S29" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 (Рыбкина), добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -2965,7 +3245,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>Данные не установлены (ПРАКТИКУМ 27, Екатеринбург, ТНП-непищевые)</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2978,44 +3258,47 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>Евгений, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Евгений, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>Евгений, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>Евгений, привет! Скажи, ?? участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Евгений, привет! Скажи, ?? участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Евгений, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -3023,89 +3306,96 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Оглоблин Александр</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Собственник сети супермаркетов «ЕЛИСЕЙ»</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Собственник сети супермаркетов «ЕЛИСЕЙ» (Екатеринбург)</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>HoReCa</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>+7 (343) 373-34-33</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/aleksandr_ogloblin</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>ogloblin@list.ru</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>https://www.elisey-mag.ru/</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>Александр, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>Александр, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>Александр, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>Александр, привет! Скажи, собственник сети супермаркетов «ЕЛИСЕЙ» участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
+Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>Александр, привет! Скажи, собственник сети супермаркетов «ЕЛИСЕЙ» участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S31" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Александр, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -3133,7 +3423,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Владелец ресторанного холдинга Good Community</t>
+          <t>Владелец Good Community: Breadway, The Barbara, Tribu, Encore Cafe, «Чаща», «Главный» (Екатеринбург)</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3141,53 +3431,64 @@
           <t>HoReCa</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 283-08-80</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/Ruslan_343</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>https://goodcom.rest/?ysclid=mmku0u9wob648838936</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>Руслан, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Руслан, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>Руслан, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>Руслан, привет! Скажи, владелец ресторанного холдинга Good Community в Ек... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
+Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>Руслан, привет! Скажи, владелец ресторанного холдинга Good Community в Екатеринбург… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Руслан, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -3195,77 +3496,80 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Пшеницын Илья</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Ген.дир ООО «Чистый Город» (автомойки)</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Ген.дир ООО «Чистый Город» (сеть автомоек Екатеринбург). Также: «Автомойки Север», «Автомойки Центр»</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Услуги для населения</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>Илья, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>Илья, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>Илья, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Событие объединяет любителей бега и предпринимателей Сколково — отличная точка для тех, кто близок к спорту и социальным проектам.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>Илья, привет! Скажи, Ген дир ООО "Чистый Город" - Компания работает в с... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>Илья, привет! Скажи, Ген дир ООО "Чистый Город" - Компания работает в сфере мойки… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S33" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Илья, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -3293,7 +3597,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Ген.дир ООО «Мотки и Бобины» (онлайн-школа)</t>
+          <t>Ген.дир ООО «Мотки и Бобины» — онлайн-школа вязания iNitki, интернет-магазин</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -3301,54 +3605,69 @@
           <t>Торговля</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>+7 800 302-19-52</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/AlexeyBardok</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>initkishop@gmail.com</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>https://get.initki.ru</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>Алексей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Алексей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>Алексей, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+Партнёрство даёт выход на топ-менеджеров крупнейшей деловой сети Сколково.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>Алексей, привет! Скажи, генеральный директор ООО «Мотки и Бобины» 
-онлайн... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
+онлайн-школы вяз… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Алексей, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Партнёрство даёт выход на топ-менеджеров крупнейшей деловой сети Сколково.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -3356,89 +3675,96 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Вражнов Сергей</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Ген.дир ООО «Производственный Склад» (складские услуги)</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Ген.дир ООО «Производственный Склад» (хранение нефтепродуктов, нефтебаза, Екатеринбург)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>Энергетика</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>+7 (343) 342-02-76</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/FreemanVSV</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>glavbuh-2011@mail.ru</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>https://proskladek.ru/?ysclid=mmlxbr7cn9506290060</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>Сергей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>Сергей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>Сергей, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>Сергей, привет! Скажи, ген дир и учредитель ООО «Производственный Склад» ... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R35" s="4" t="inlineStr">
+        <is>
+          <t>Сергей, привет! Скажи, ген дир и учредитель ООО «Производственный Склад» - Хранение… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S35" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Сергей, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -3466,7 +3792,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Ген.дир ООО «Персона Грата» (офисная мебель)</t>
+          <t>Ген.дир ООО «Персона Грата» (оптовая торговля офисной мебелью, Екатеринбург)</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3476,59 +3802,66 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>+7 (343) 371-18-30</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
+          <t>+7 (343) 222-14-22</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/Lorigina</t>
+        </is>
+      </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
           <t>kon@grata-mebel.ru</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>https://grata-mebel.ru</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>Регина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Регина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>Регина, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>Регина, привет! Скажи, ген дир и учредитель ООО «Персона Грата» - оптовая... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>Регина, привет! Скажи, ген дир и учредитель ООО «Персона Грата» - оптовая торговля … участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Регина, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -3536,90 +3869,97 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Калетин Андрей</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Основатель и ген.дир холдинга «ЭМА»</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Основатель и ген.дир холдинга «ЭМА» (добыча, строительство, медоборудование, агро). Блог: vc.ru/id3811985</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>Производство</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>+7 (343) 300-40-11</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/Kaaandrey96</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>info@ema.su</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>https://emaholding.ru</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>Андрей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>Андрей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>Андрей, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
         <is>
           <t>Андрей, привет! Скажи, основатель и руководитель холдинга «ЭМА»
-Холдинг ... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
+Холдинг «ЭМА» осно… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S37" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Андрей, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -3647,7 +3987,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Основатель и ген.дир 19agency84 (креативно-диджитал агентство)</t>
+          <t>Основатель и ген.дир 19agency84 (бренды, digital, SMM, SEO, Екатеринбург)</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3660,7 +4000,11 @@
           <t>+7 (343) 305-19-84</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/thekatyamarkova</t>
+        </is>
+      </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
           <t>newbusiness@19agency84.com</t>
@@ -3671,49 +4015,56 @@
           <t>https://vk.com/19agency84</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>https://tenchat.ru/0515730</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>https://19agency84.ru</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>Екатерина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Екатерина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>Екатерина, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>Екатерина, привет! Скажи, основатель и генеральный директор креативно-диджит... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
+Партнёрство даёт выход на топ-менеджеров крупнейшей деловой сети Сколково.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Екатерина, привет! Скажи, основатель и генеральный директор креативно-диджитал-агентст… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Екатерина, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Партнёрство даёт выход на топ-менеджеров крупнейшей деловой сети Сколково.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -3721,77 +4072,84 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Орлова Екатерина</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Предприниматель (прежние компании ликвидированы)</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Предприниматель (медиа/маркетинг, Екатеринбург). Прежние компании ликвидированы</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>СМИ, реклама и маркетинг</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/orlova_ka</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Екатерина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>Екатерина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>Екатерина, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>Екатерина, привет! Скажи, бывший генеральный директор ликвидированных компан... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>Екатерина, привет! Скажи, бывший генеральный директор ликвидированных компаний «БИГ МЕ… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S39" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Екатерина, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -3819,7 +4177,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Директор ООО «Пром Сервис»</t>
+          <t>Директор ООО «Пром Сервис» (оптовая торговля ломом и отходами, Екатеринбург)</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3832,56 +4190,63 @@
           <t>+7 (343) 380-99-41</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/mikhailvsn</t>
+        </is>
+      </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
           <t>info@promservice-ek.ru</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>https://p-service.pro</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Михаил, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Михаил, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>Михаил, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>Михаил, привет! Скажи, директор и единственный учредитель ООО «Пром Серви... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>Михаил, привет! Скажи, директор и единственный учредитель ООО «Пром Сервис» - заним… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Михаил, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -3889,78 +4254,89 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Михалицын Андрей</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>https://frame-expert.ru/?ysclid=mmlxy1japz736537895</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Ген.дир ООО «ФРЕЙМ» (строительство)</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Рук. ООО «ФРЕЙМ» (стройэкспертиза, проектная документация) + ООО «МАН ГРУПП» (бетон, manbeton.ru)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>Строительство, недвижимость, проектирование</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/mixalitsin</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="inlineStr"/>
+      <c r="M41" s="4" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>https://frame-expert.ru/</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Андрей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>Андрей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>Андрей, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
         <is>
           <t>Андрей, привет! Скажи, 1) руководитель и учредитель ООО «ФРЕЙМ» - 
-Провод... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
+Проводим строите… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S41" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Андрей, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -3988,7 +4364,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Учредитель ООО «ГРИТ» (строительство жилых домов)</t>
+          <t>Учредитель ООО «ГРИТ» (строительство), «НОВАЯ МАГИСТРАЛЬ» (дороги), «ДЕВАЙС» (логистика)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -4001,48 +4377,55 @@
           <t>7 922 209 0155</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/OEduard</t>
+        </is>
+      </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>Эдуард, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Эдуард, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>Эдуард, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>Эдуард, привет! Скажи, 1) Учредитель ООО «ГРИТ» - занимается строительств... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Эдуард, привет! Скажи, 1) Учредитель ООО «ГРИТ» - занимается строительством жилых и… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Эдуард, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -4050,89 +4433,96 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Петров Константин</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Ген.дир ООО «Микроклимат» (вентиляционные системы)</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Ген.дир ООО «Микроклимат» (системы вентиляции для животноводческих комплексов)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>Производство</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>+7 800 600 71 98</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/ventilator82</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>info@micro-climate.com</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>https://micro-climate.com/blog/avtory-bloga/konstantin-petrov</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>Константин, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>Константин, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
         <is>
           <t>Константин, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>Константин, привет! Скажи, генеральный директор и учредитель ООО «Микроклимат... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R43" s="4" t="inlineStr">
+        <is>
+          <t>Константин, привет! Скажи, генеральный директор и учредитель ООО «Микроклимат» -   прои… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S43" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Константин, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -4160,7 +4550,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Директор ООО «РЕСУРС» (стройматериалы, Набережные Челны)</t>
+          <t>Директор ООО «РЕСУРС» (стройматериалы, бетонные изделия, Набережные Челны)</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -4173,44 +4563,47 @@
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>Александр, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Александр, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>Александр, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>Александр, привет! Скажи, ООО «РЕСУРС» - Основной вид деятельности — оптовая... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
+Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Александр, привет! Скажи, ООО «РЕСУРС» - Основной вид деятельности — оптовая торговля … участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Александр, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -4218,89 +4611,93 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Измайлова Марина</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Управляющий собственник ГК «СтандартПродМаш» (пищевые производства)</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Управляющий собственник ГК «СтандартПродМаш» (пищевое производство и оборудование, Казань)</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>Промышленное оборудование, техника, станки и комплектующие</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>+7 960 055 4868</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>+7 (937) 612-79-68</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>sale@press-forms.ru</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>https://marinaizmaylova.ru/?ysclid=mm3cma7f93941258765</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>Марина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>Марина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
         <is>
           <t>Марина, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>Марина, привет! Скажи, Эксперт в сфере создания рентабельных пищевых прои... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R45" s="4" t="inlineStr">
+        <is>
+          <t>Марина, привет! Скажи, Эксперт в сфере создания рентабельных пищевых производств
+ПО… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S45" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Марина, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -4328,7 +4725,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Министр экологии и природных ресурсов Республики Татарстан</t>
+          <t>Бывший Министр экологии РТ; в 2026 — директор Департамента водных ресурсов Минприроды РФ</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4348,49 +4745,52 @@
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>eco.tatarstan.ru</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>https://eco.tatarstan.ru</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>Александр, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Александр, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>Александр, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Мероприятие проводится совместно со Сколково — открыты к партнёрству с организациями, которые развивают социальные и инвестиционные проекты.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>Александр, привет! Скажи, Министр экологии и природных ресурсов Республики Т... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Александр, привет! Скажи, Министр экологии и природных ресурсов Республики Татарстан. участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Александр, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -4398,89 +4798,93 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Яковлев Станислав</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Президент Федерации скалолазания Республики Татарстан</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Президент Федерации скалолазания РТ. Адрес: ул. Дубравная, 2Б, оф. 4, Казань</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Строительство, недвижимость, эксплуатация, проектирование</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>+7 996 644 9436</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>+7 (843) 265-55-88</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>info@fctat.ru</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>https://fctat.ru/federation/sotrudniki/yakovlev-stanislav-igorevich/?ysclid=mm3cten8ms666573853</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>Станислав, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>Станислав, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
         <is>
           <t>Станислав, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>Станислав, привет! Скажи, 1) президент Федерации скалолазания Республики Тат... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R47" s="4" t="inlineStr">
+        <is>
+          <t>Станислав, привет! Скажи, 1) президент Федерации скалолазания Республики Татарстан
+2) … участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S47" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Станислав, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -4508,7 +4912,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Предприниматель (компания ликвидирована, Казань)</t>
+          <t>Предприниматель (Казань/Набережные Челны). Управляет ООО ПКФ «РОСТ» (ИНН 165031102860)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -4521,44 +4925,47 @@
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>Ильнар, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Ильнар, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>Ильнар, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>Ильнар, привет! Скажи, ликвидирована участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>Ильнар, привет! Скажи, ликвидирована участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Ильнар, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -4566,90 +4973,93 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Липатов Александр</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Учредитель ООО «ТСС ЭНЕРДЖИ» (инжиниринг)</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Учредитель ООО «ТСС ЭНЕРДЖИ» (электромонтаж, слаботочные сети, Казань)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>Энергетика</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>+7 (843) 590-36-30</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>info@tssenergy.ru</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>tssenergy.ru</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr"/>
+      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>https://tssenergy.ru</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>Александр, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>Александр, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr">
         <is>
           <t>Александр, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R49" s="4" t="inlineStr">
         <is>
           <t>Александр, привет! Скажи, Учредитель ООО «ТСС ЭНЕРДЖИ" - 
-Компания выполняет... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
+Компания выполняет полный ци… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S49" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Александр, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -4677,7 +5087,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Исполнительный директор Федерации шахмат РТ</t>
+          <t>Исполнительный директор Федерации шахмат РТ. ул. Бутлерова, 7, каб. 47, Казань</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -4697,49 +5107,52 @@
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>tat-chess.ru</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>https://tat-chess.ru</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>Ильдар, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Ильдар, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>Ильдар, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Событие объединяет любителей бега и предпринимателей Сколково — отличная точка для тех, кто близок к спорту и социальным проектам.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>Ильдар, привет! Скажи, исполнительный директор федерации шахмат Татарстан... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
+Событие объединяет спорт и бизнес-сообщество — отличный формат для тех, кто любит активность.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>Ильдар, привет! Скажи, исполнительный директор федерации шахмат Татарстана участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Ильдар, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие объединяет спорт и бизнес-сообщество — отличный формат для тех, кто любит активность.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -4747,77 +5160,84 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Нагуманов Адель</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>Предприниматель (ИП ликвидирован, Казань)</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Ген.дир ООО «Экспос Груп» (организация выставок, выручка 240 млн ₽, Казань)</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>Общественная деятельность, партии, благотворительность, НКО</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>kipchak2004@mail.ru</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr"/>
+      <c r="L51" s="4" t="inlineStr"/>
+      <c r="M51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr"/>
+      <c r="O51" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>Адель, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>Адель, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
         <is>
           <t>Адель, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>Адель, привет! Скажи, ликвидирована участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R51" s="4" t="inlineStr">
+        <is>
+          <t>Адель, привет! Скажи, ликвидирована участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S51" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Адель, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -4845,7 +5265,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Ген.дир ООО «ЭВО-ХАУС» (аренда недвижимости, Казань)</t>
+          <t>Ген.дир ООО «ЭВО-ХАУС» (аренда и управление недвижимостью, Казань)</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -4858,44 +5278,47 @@
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>Арина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>Арина, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>Арина, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>Арина, привет! Скажи, 1) Ген дир - ООО «ЭВО-ХАУС» занимается арендой и у... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>Арина, привет! Скажи, 1) Ген дир - ООО «ЭВО-ХАУС» занимается арендой и управлением… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Арина, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -4903,77 +5326,80 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Кузнецова Елена</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>Специалист по бухгалтерским/финансовым услугам (Казань)</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Специалист по бухгалтерским/финансовым услугам (Казань). Точные данные не установлены</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>Услуги для населения</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr"/>
+      <c r="J53" s="4" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr"/>
+      <c r="L53" s="4" t="inlineStr"/>
+      <c r="M53" s="4" t="inlineStr"/>
+      <c r="N53" s="4" t="inlineStr"/>
+      <c r="O53" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>Елена, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P53" s="4" t="inlineStr">
+        <is>
+          <t>Елена, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="inlineStr">
         <is>
           <t>Елена, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>Елена, привет! Скажи, оказание услуг в области бухгалтерского учёта, фин... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
+Аудитория события — инвесторы и собственники из сети Сколково.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R53" s="4" t="inlineStr">
+        <is>
+          <t>Елена, привет! Скажи, оказание услуг в области бухгалтерского учёта, финансового а… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S53" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Елена, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Аудитория события — инвесторы и собственники из сети Сколково.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -5018,44 +5444,47 @@
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>Рустем, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>Рустем, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>Рустем, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>Рустем, привет! Скажи, Ген дир и учредитель ООО «Клиника здоровья и красо... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>Рустем, привет! Скажи, Ген дир и учредитель ООО «Клиника здоровья и красоты» (г. Ка… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Рустем, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -5063,81 +5492,84 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>Мулюков Ильдар</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>Директор ООО «ТРИТОН ИНВЕСТ» (инвестиции/недвижимость, Казань)</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Директор ООО «ТРИТОН ИНВЕСТ» + ООО «Тритон Трейд» (торговля топливом, выручка 32 млрд ₽, Казань)</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>Строительство, недвижимость, эксплуатация, проектирование</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>ildar.mn82@gmail.com</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>Ильдар, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P55" s="4" t="inlineStr">
+        <is>
+          <t>Ильдар, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="inlineStr">
         <is>
           <t>Ильдар, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>Ильдар, привет! Скажи, 1) Директор ООО "ТРИТОН ИНВЕСТ - ООО «ТРИТОН ИНВЕС... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R55" s="4" t="inlineStr">
+        <is>
+          <t>Ильдар, привет! Скажи, 1) Директор ООО "ТРИТОН ИНВЕСТ - ООО «ТРИТОН ИНВЕСТ» (г. Каз… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S55" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Ильдар, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -5165,7 +5597,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Ген.дир My Corner by Unistroy (застройщик)</t>
+          <t>Ген.дир My Corner by Unistroy (один из крупнейших застройщиков РТ, Казань)</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -5185,49 +5617,56 @@
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/corniloff-anton-2174</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>https://ya.ru/search/?text=My+CORNER+by+Unistroy&amp;lr=213&amp;search_source=yaru_desktop_common&amp;search_domain=yaru</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>Антон, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Антон, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>Антон, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>Антон, привет! Скажи, Ген дир компании My Corner by Unistroy – один из к... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Антон, привет! Скажи, Ген дир компании My Corner by Unistroy – один из крупнейших … участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Антон, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -5235,77 +5674,92 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>Лекарев Илья</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>Предприниматель (компания ликвидирована, Казань)</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Директор ООО «АК БАРС ИНЖИНИРИНГ» и ООО «СИТИ ПРОЕКТ» (Казань)</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>Строительство, недвижимость, эксплуатация, проектирование</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>+7 (843) 205-49-90</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>ABIReception@abdev.ru</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="inlineStr"/>
+      <c r="M57" s="4" t="inlineStr"/>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>https://akbars-eng.ru</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>Илья, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P57" s="4" t="inlineStr">
+        <is>
+          <t>Илья, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="inlineStr">
         <is>
           <t>Илья, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>Илья, привет! Скажи, ликвидирована участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R57" s="4" t="inlineStr">
+        <is>
+          <t>Илья, привет! Скажи, ликвидирована участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S57" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Илья, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -5333,7 +5787,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Предприниматель (ИП ликвидирован, Казань)</t>
+          <t>Предприниматель (Казань/Сабинский р-н РТ). Консалтинг, строительство, недвижимость</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -5342,48 +5796,55 @@
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/azatm016</t>
+        </is>
+      </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>Азат, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>Азат, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
         <is>
           <t>Азат, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>Азат, привет! Скажи, ип ликвидирован участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>Азат, привет! Скажи, ип ликвидирован участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Азат, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -5391,81 +5852,100 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>Муртазин Ленар</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>Основатель агентства «Неко-Франч» (франчайзинг), Казань</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Основатель «Неко-Франч» (франчайзинг, упаковка бизнесов), сопредседатель «Деловой России» РТ</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>Строительство, недвижимость, эксплуатация, проектирование</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>nekofranch.ru</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>+7 (917) 919-43-60</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/lenarmurtaz</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>sales@nekofranch.ru</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr"/>
+      <c r="L59" s="4" t="inlineStr"/>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>https://tenchat.ru/0468718</t>
+        </is>
+      </c>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>https://nekofranch.ru</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>Ленар, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P59" s="4" t="inlineStr">
+        <is>
+          <t>Ленар, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="inlineStr">
         <is>
           <t>Ленар, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>Ленар, привет! Скажи, ип ликвидирован участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R59" s="4" t="inlineStr">
+        <is>
+          <t>Ленар, привет! Скажи, ип ликвидирован участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S59" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Ленар, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -5493,7 +5973,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Руководитель Агентства инвестиционного развития РТ</t>
+          <t>Руководитель Агентства инвестиционного развития Республики Татарстан</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -5513,49 +5993,52 @@
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>tida.tatarstan.ru</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>https://tida.tatarstan.ru</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>Талия, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Талия, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
         <is>
           <t>Талия, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>Талия, привет! Скажи, Руководитель Агентства инвестиционного развития Ре... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
+Аудитория события — инвесторы и собственники из сети Сколково.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>Талия, привет! Скажи, Руководитель Агентства инвестиционного развития Республики Т… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Талия, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Аудитория события — инвесторы и собственники из сети Сколково.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -5563,93 +6046,100 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Денисов Виталий</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>Сооснователь Imagine Group (событийный маркетинг)</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Сооснователь и директор Imagine Group (событийный маркетинг, Казань)</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>СМИ, маркетинг, реклама, BTL, PR, дизайн, продюсирование</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>+7 800 700 5140</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>@IMG_Event</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>https://t.me/IMG_Event</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>hello@imgevent.ru</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr"/>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/denisov-vitaliy-19968bb1</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr"/>
+      <c r="N61" s="4" t="inlineStr">
         <is>
           <t>https://imgevent.ru/o-nas</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="O61" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>Виталий, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P61" s="4" t="inlineStr">
+        <is>
+          <t>Виталий, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="inlineStr">
         <is>
           <t>Виталий, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>Виталий, привет! Скажи, сооснователь и руководитель агентства Imagine Grou... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>Виталий, привет! Скажи, сооснователь и руководитель агентства Imagine Group участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S61" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Виталий, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -5677,7 +6167,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Сооснователь Imagine Group (событийный маркетинг)</t>
+          <t>Сооснователь Imagine Group (Гузеев Роман Валериевич). Личный TG: @imagineyourbest (возможно рабочий)</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -5692,7 +6182,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>@IMG_Event</t>
+          <t>https://t.me/IMG_Event</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -5701,49 +6191,52 @@
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>https://imgevent.ru/o-nas</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>Роман, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>Роман, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
         <is>
           <t>Роман, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>Роман, привет! Скажи, сооснователь и руководитель агентства Imagine Grou... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>Роман, привет! Скажи, сооснователь и руководитель агентства Imagine Group участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Роман, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -5751,86 +6244,93 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Нижний Новгород</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>Боткин Евгений</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>Нижний Новгород</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>Ген.дир ООО НПП «Вита-Принт» (полиграфия)</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Ген.дир ООО НПП «Вита-Принт» (промышленная печать, электроника, Нижний Новгород). Доп. тел: +7 910 393-47-17</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>Электроника, приборостроение, бытовая техника, компьютеры и оргтехника</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>+7 (831) 412-32-17</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>vita@kis.ru</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>vita-print.com</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="J63" s="4" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr"/>
+      <c r="L63" s="4" t="inlineStr"/>
+      <c r="M63" s="4" t="inlineStr"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>https://vita-print.com</t>
+        </is>
+      </c>
+      <c r="O63" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>Евгений, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>Евгений, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="inlineStr">
         <is>
           <t>Евгений, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R63" s="4" t="inlineStr">
         <is>
           <t>Евгений, привет! Скажи, генеральный директор ООО НПП «Вита-Принт»
-Компания... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
+Компания занимаетс… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S63" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Евгений, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -5858,7 +6358,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Учредитель ООО «ГЛОБАЛТЕСТ» (Нижний Новгород/Саров)</t>
+          <t>Учредитель ООО «ГЛОБАЛТЕСТ» (Нижний Новгород / Саров). ИНН 525405005570</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -5878,49 +6378,52 @@
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>globaltest.ru</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>https://globaltest.ru</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>Никита, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>Никита, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
         <is>
           <t>Никита, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>Никита, привет! Скажи, Учредитель ООО «ГЛОБАЛТЕСТ». Компания зарегистриро... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>Никита, привет! Скажи, Учредитель ООО «ГЛОБАЛТЕСТ». Компания зарегистрирована в Сар… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Никита, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -5928,89 +6431,92 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Нижний Новгород</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Комиссаров Евгений</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>г. Дзержинск</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>Директор ООО «ПТС НН» (автозапчасти)</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Директор ООО «ПТС НН» (автозапчасти, Нижний Новгород). Профиль nn.ru: Evgen52 (07.07.1988)</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>Автомобильный бизнес</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>+7 (831) 276-16-45</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>alexandr@ptsnn.com</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>ptsnn.com</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>gto@pts-nn.ru</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr"/>
+      <c r="M65" s="4" t="inlineStr"/>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>https://ptsnn.com</t>
+        </is>
+      </c>
+      <c r="O65" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>Евгений, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>Евгений, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="inlineStr">
         <is>
           <t>Евгений, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Событие объединяет любителей бега и предпринимателей Сколково — отличная точка для тех, кто близок к спорту и социальным проектам.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>Евгений, привет! Скажи, 1) ООО «ПТС НН» - розничная торговля автомобильным... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R65" s="4" t="inlineStr">
+        <is>
+          <t>Евгений, привет! Скажи, 1) ООО «ПТС НН» - розничная торговля автомобильными деталями… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S65" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Евгений, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -6038,7 +6544,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Сооснователь GASTREET International Restaurant Show / HORECA HUB</t>
+          <t>Сооснователь GASTREET Int. Restaurant Show / запустила HORECA HUB (Сочи)</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -6049,54 +6555,61 @@
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>@sufianova_ru</t>
+          <t>https://t.me/sufianova_ru</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sufiyanovae</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>Ожидается, что с 7 по 12 июня 2026 года Gastreet International Restaurant Show пройдёт в Сочи. В мероприятии планируют принять участие более 5500 профессионалов — предпринимателей, рестораторов, шеф-поваров и экспертов, которые влияют на развитие ресторанной сферы в России</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>Евгения, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>Евгения, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
         <is>
           <t>Евгения, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>Евгения, привет! Скажи, сооснователь и генеральный продюсер GASTREET Inter... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>Евгения, привет! Скажи, сооснователь и генеральный продюсер GASTREET International R… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Евгения, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -6104,89 +6617,92 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Краснодарский край</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>Трукшин Вадим</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>Сочи</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>Ген.дир группы MANTERA (курорты Красная Поляна, Архыз)</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Ген.дир группы MANTERA (курорты Красная Поляна, Архыз, назначен окт. 2023)</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>HoReCa</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>8 800 100 78 62</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>mice@mantera-group.com</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="J67" s="4" t="inlineStr"/>
+      <c r="K67" s="4" t="inlineStr"/>
+      <c r="L67" s="4" t="inlineStr"/>
+      <c r="M67" s="4" t="inlineStr"/>
+      <c r="N67" s="4" t="inlineStr">
         <is>
           <t>https://mantera.ru/company/?ysclid=mltqh7zsxm824389413</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="O67" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>Вадим, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P67" s="4" t="inlineStr">
+        <is>
+          <t>Вадим, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q67" s="4" t="inlineStr">
         <is>
           <t>Вадим, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>Вадим, привет! Скажи, генеральный директор группы Mantera, одного из кру... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P67" s="2" t="inlineStr">
+Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R67" s="4" t="inlineStr">
+        <is>
+          <t>Вадим, привет! Скажи, генеральный директор группы Mantera, одного из крупнейших ту… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S67" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Вадим, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -6214,7 +6730,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Директор ООО «АЛЬФА-СЕРВИС» (Сочи)</t>
+          <t>Директор ООО «АЛЬФА-СЕРВИС» (Сочи, ИНН 2319051740)</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -6231,44 +6747,47 @@
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>Анфиса, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Анфиса, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
         <is>
           <t>Анфиса, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Это живой контакт с людьми, которые принимают решения о партнёрстве.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>Анфиса, привет! Скажи, ООО «АЛЬФА-СЕРВИС - Компания зарегистрирована в Со... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="inlineStr">
+Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>Анфиса, привет! Скажи, ООО «АЛЬФА-СЕРВИС - Компания зарегистрирована в Сочи и работ… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Анфиса, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Ваша аудитория и наша — очень близки: предприниматели, которые ценят качество и активный образ жизни.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -6276,89 +6795,92 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Краснодарский край</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>Перов Павел</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>Сочи</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>Ген.дир курорта «Красная Поляна», первый замгендира ГК «Мантера»</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Ген.дир курорта «Красная Поляна», первый замген.дир ГК «Мантера» (с 28.06.2024)</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
         <is>
           <t>Услуги для населения</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>+7 800 550 20 20</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="H69" s="4" t="inlineStr"/>
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>infocenter@kpresort.ru</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>krasnayapolyanaresort.ru</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="J69" s="4" t="inlineStr"/>
+      <c r="K69" s="4" t="inlineStr"/>
+      <c r="L69" s="4" t="inlineStr"/>
+      <c r="M69" s="4" t="inlineStr"/>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>https://krasnayapolyanaresort.ru</t>
+        </is>
+      </c>
+      <c r="O69" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>Павел, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P69" s="4" t="inlineStr">
+        <is>
+          <t>Павел, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q69" s="4" t="inlineStr">
         <is>
           <t>Павел, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Это событие с понятной социальной миссией и хорошей деловой аудиторией — сообщество выпускников и слушателей Школы управления Сколково.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>Павел, привет! Скажи, новый генеральный директор курорта «Красная Поляна... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="inlineStr">
+Участники забега — именно та аудитория, которой интересны активный отдых и путешествия.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R69" s="4" t="inlineStr">
+        <is>
+          <t>Павел, привет! Скажи, новый генеральный директор курорта «Красная Поляна» в Сочи участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S69" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Павел, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Участники забега — именно та аудитория, которой интересны активный отдых и путешествия.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -6386,7 +6908,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Директор ООО «И-ТУР» (туризм, Сочи)</t>
+          <t>Директор ООО «И-ТУР» (туризм/недвижимость, Сочи). TenChat: @irik_sochi</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -6399,45 +6921,52 @@
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>https://tenchat.ru/irik_sochi</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>Ирик, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>Ирик, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
         <is>
           <t>Ирик, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
+Участники забега — именно та аудитория, которой интересны активный отдых и путешествия.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
         <is>
           <t>Ирик, привет! Скажи, директор и учредитель ООО «И-ТУР» 
-Основной вид де... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="inlineStr">
+Основной вид деятельности… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Ирик, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Участники забега — именно та аудитория, которой интересны активный отдых и путешествия.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -6445,89 +6974,92 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>Краснодарский край</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>Барачина Надежда</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>Замглавы правления и ген.дир Alias Group (девелопмент, Краснодар)</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Замглавы правления и ген.дир Alias Group (девелопер «Неометрия», портфель 70 млрд ₽, Краснодар)</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>Строительство, недвижимость, эксплуатация, проектирование</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>+7 861 205-09-84</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" s="5" t="inlineStr">
         <is>
           <t>info@alias-group.ru</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>alias-group.ru</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
+      <c r="J71" s="4" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr"/>
+      <c r="L71" s="4" t="inlineStr"/>
+      <c r="M71" s="4" t="inlineStr"/>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>https://alias-group.ru</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>Надежда, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P71" s="4" t="inlineStr">
+        <is>
+          <t>Надежда, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q71" s="4" t="inlineStr">
         <is>
           <t>Надежда, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>Надежда, привет! Скажи, заместитель председателя правления, генеральный ди... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R71" s="4" t="inlineStr">
+        <is>
+          <t>Надежда, привет! Скажи, заместитель председателя правления, генеральный директор инв… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S71" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Надежда, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -6555,7 +7087,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Ген.дир ООО «АА ПАРТНЕРС» / FOCUS Management (девелопмент)</t>
+          <t>Ген.дир «АА ПАРТНЕРС» / FOCUS Management (дизайн интерьеров HoReCa, девелопмент, Краснодар)</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -6573,47 +7105,54 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>aa-partners.ru</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
+          <t>https://instagram.com/aa_partners</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>https://aa-partners.ru</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>Анна, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>Анна, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
         <is>
           <t>Анна, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>Анна, привет! Бизнес участвует в благотворительных или спортивных проектах?
-Есть интересный формат участия в событии фонда «БольшеЧемМожешь» совместно со Сколково в июне — хочу понять, есть ли смысл рассказать подробнее.</t>
-        </is>
-      </c>
-      <c r="P72" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>Анна, привет! Ваш бизнес участвует в благотворительных или спортивных проектах?
+Есть интересный формат участия в событии фонда «БольшеЧемМожешь» совместно со Сколково в июне — стоит ли рассказать подробнее?</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Анна, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -6621,89 +7160,96 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>Краснодарский край</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>Манькова Инна</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>Директор ООО «ЧФК-Недвижимость» (инвестиции, Краснодар)</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Директор ООО «ЧФК-Недвижимость» (инвестиции в жилую недвижимость, Краснодар)</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>Строительство, недвижимость, эксплуатация, проектирование</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>8 800 700 1800</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>bsfc@bsfc.com</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>bsfc.com</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>https://vk.com/bsfckrd</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr"/>
+      <c r="L73" s="4" t="inlineStr"/>
+      <c r="M73" s="4" t="inlineStr"/>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>https://bsfc.com</t>
+        </is>
+      </c>
+      <c r="O73" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>Инна, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P73" s="4" t="inlineStr">
+        <is>
+          <t>Инна, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="inlineStr">
         <is>
           <t>Инна, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>Инна, привет! Скажи, директор ООО «ЧФК — Недвижимость: компания в сфере... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P73" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R73" s="4" t="inlineStr">
+        <is>
+          <t>Инна, привет! Скажи, директор ООО «ЧФК — Недвижимость: компания в сфере инвестици… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S73" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Инна, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -6731,7 +7277,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Директор ООО «Ванвин» (производство витаминов/БАД)</t>
+          <t>Директор ООО «Ванвин» + ООО «Ванвин Групп» + ООО «Со Лаб» (витамины/БАД, выручка 205 млн ₽)</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -6748,44 +7294,51 @@
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>https://modern-vitamins.ru</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>Алексей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>Алексей, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
         <is>
           <t>Алексей, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Событие объединяет любителей бега и предпринимателей Сколково — отличная точка для тех, кто близок к спорту и социальным проектам.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O74" s="2" t="inlineStr">
-        <is>
-          <t>Алексей, привет! Скажи, ООО «Ванвин»  — один из лидеров в создании качеств... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P74" s="2" t="inlineStr">
+Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>Алексей, привет! Скажи, ООО «Ванвин»  — один из лидеров в создании качественных вита… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Алексей, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Это деловое сообщество Сколково: 300+ участников, предприниматели и топ-менеджеры из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -6793,81 +7346,84 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Краснодарский край</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Рунец Роман</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>Ген.дир ООО «ИТР» (IT/строительство дорог, Краснодар)</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Ген.дир ООО «ИТР» (ИТС для дорог) + директор по развитию ООО «ЦДИ» (Краснодар, с 2025)</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>Строительство, недвижимость, эксплуатация, проектирование</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr"/>
+      <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr"/>
+      <c r="J75" s="4" t="inlineStr"/>
+      <c r="K75" s="4" t="inlineStr"/>
+      <c r="L75" s="4" t="inlineStr"/>
+      <c r="M75" s="4" t="inlineStr"/>
+      <c r="N75" s="4" t="inlineStr">
         <is>
           <t>https://itr2050.ru/komanda.html</t>
         </is>
       </c>
-      <c r="L75" s="2" t="inlineStr">
+      <c r="O75" s="4" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>Роман, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P75" s="4" t="inlineStr">
+        <is>
+          <t>Роман, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="inlineStr">
         <is>
           <t>Роман, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="inlineStr">
-        <is>
-          <t>Роман, привет! Скажи, ооо итр: Предоставляем полный комплекс услуг для р... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P75" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R75" s="4" t="inlineStr">
+        <is>
+          <t>Роман, привет! Скажи, ооо итр: Предоставляем полный комплекс услуг для разработки … участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S75" s="4" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Роман, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -6895,7 +7451,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Директор ООО СК «Екатеринодар-Сити» (строительство)</t>
+          <t>Директор ООО СК «Екатеринодар-Сити» (строительство жилых зданий, Краснодар, ~403 млн ₽)</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -6908,44 +7464,47 @@
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
         </is>
       </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>Игорь, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>Игорь, привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
         <is>
           <t>Игорь, добрый день! Влад из фонда «БольшеЧемМожешь».
 Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Партнёрство даёт реальное присутствие бренда среди деловой аудитории Сколково — собственников и топов из разных регионов.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>Игорь, привет! Скажи, директор ООО СК «Екатеринодар-Сити», занимающегося... участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-      <c r="P76" s="2" t="inlineStr">
+Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Есть партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>Игорь, привет! Скажи, директор ООО СК «Екатеринодар-Сити», занимающегося строитель… участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
         <is>
           <t>Тема: Партнёрство на «Сколковской миле» — 20 июня 2026, кампус Сколково
 Игорь, добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле, флаги, упоминание ведущим 6 раз)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — забег на крыше кампуса. Событие собирает деловую аудиторию Сколково — собственников и топов из разных регионов.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (пресс-волл, флаги, 6 упоминаний ведущим)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
 • Амбассадор старта — 100 000 ₽
-Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
+Готов прислать презентацию. Можем созвониться на 15 минут?
 С уважением,
 Владислав
 Фонд «БольшеЧемМожешь» | morethanable.ru</t>
@@ -6953,6 +7512,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:S1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6966,87 +7526,87 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Формат</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="200" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>TELEGRAM / VK
-Вариант 1 — Короткий тёплый первый контакт
-(рекомендуется для первого сообщения)</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>[Имя], привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — мы помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Текст / Рекомендации</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="250" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>TELEGRAM / ВКОНТАКТЕ
+Вариант 1 — Тёплый первый контакт
+(рекомендуется для начала)</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>[Имя], привет! Меня зовут Влад, я представляю фонд «БольшеЧемМожешь» — помогаем людям с ДЦП участвовать в марафонах и вести активную жизнь.
 20 июня в Москве проводим «Сколковскую милю» — благотворительный забег на крыше кампуса МШУ Сколково. 300+ участников, охват 20 000+.
-Есть несколько форматов участия для бизнеса — от брендинга на старте до зоны с гостями. Можно пообщаться пару минут?</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="200" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>TELEGRAM / VK
+Есть форматы участия для бизнеса — от брендинга до зоны с гостями. Можно пообщаться пару минут?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="250" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>TELEGRAM / ВКОНТАКТЕ
 Вариант 2 — Акцент на деловую аудиторию
-(если нет ответа на вар. 1 — отправить через 2-3 дня)</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
+(если нет ответа — через 2-3 дня)</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>[Имя], добрый день! Влад из фонда «БольшеЧемМожешь».
-Мы с командой Сколково проводим «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
-Аудитория события — предприниматели и топ-менеджеры из сети Сколково. Партнёрство даёт живой контакт с людьми, которые принимают решения.
-Есть пакеты от 100 000 до 800 000 руб. Готов коротко рассказать — удобно?</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="200" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>TELEGRAM / VK
-Вариант 3 — Диалоговый вопрос (самый мягкий)
-(альтернатива вар. 1 для холодной базы)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>[Имя], привет! Скажи, ваш бизнес участвует в каких-то благотворительных проектах или корпоративных спортивных активностях?
-Спрашиваю, потому что у нас есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли будет обсудить.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="200" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+Мы с командой Сколково организуем «Сколковскую милю» 20 июня — благотворительный забег в кампусе.
+[Контекст под аудиторию из таблицы — вар. 2 персонализирован]
+Партнёрские пакеты от 100 000 до 800 000 ₽. Готов коротко рассказать — удобно?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="250" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>TELEGRAM / ВКОНТАКТЕ
+Вариант 3 — Диалоговый вопрос (лучший отклик)
+(самый мягкий, особенно для «холодных»)</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>[Имя], привет! Скажи, [компания] участвует в благотворительных или корпоративных спортивных проектах?
+Есть интересный формат участия в июньском событии совместно со Сколково — хочу понять, актуально ли обсудить.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="250" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>EMAIL
-Тема письма: Партнёрство на «Сколковской миле» — 20 июня 2026</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+Тема: Партнёрство на «Сколковской миле» — 20 июня 2026</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>[Имя], добрый день!
-Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Мы помогаем людям с ДЦП и другими неврологическими заболеваниями участвовать в спортивных мероприятиях — более 190 подопечных, 500 волонтёров.
-20 июня 2026 года совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
-Мы ищем партнёров мероприятия и предлагаем несколько форматов участия:
-• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле и флагах, упоминание ведущим 6 раз, дайджест аудитории Сколково)
+Меня зовут Владислав, я фандрайзер Благотворительного фонда «БольшеЧемМожешь» (morethanable.ru). Помогаем людям с ДЦП и неврологическими заболеваниями участвовать в спортивных мероприятиях — 190+ подопечных, 500 волонтёров.
+20 июня 2026 совместно со Школой управления СКОЛКОВО проводим «Сколковскую милю» — благотворительный забег на крыше кампуса. Ожидается 300+ участников, медиаохват 20 000+.
+Форматы участия:
+• Генеральный партнёр — 800 000 ₽ (логотип на пресс-волле и флагах, упоминание ведущим 6 раз, рассылка по участникам)
 • Партнёр — 500 000 ₽
 • «При поддержке» — 300 000 ₽
-• Амбассадор старта — 100 000 ₽ (упоминание ведущим + логотип в пост-релизе)
+• Амбассадор старта — 100 000 ₽ (упоминание + логотип в пост-релизе)
 Готов прислать презентацию и ответить на вопросы. Можем созвониться на 15–20 минут?
 С уважением,
 Владислав
@@ -7054,34 +7614,44 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="200" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>РЕКОМЕНДАЦИИ ПО СТРАТЕГИИ</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>1. ПОРЯДОК ДЕЙСТВИЙ:
-   День 1 → Отправь Вариант 1 или 3 в TG/VK
-   День 3-4 → Если нет ответа — дублируй на email
-   День 6-7 → Если нет ответа — Вариант 2 в мессенджер (1 раз)
-   После → Не преследуй. Максимум 3 касания.
-2. ПЕРСОНАЛИЗАЦИЯ (обязательно!):
-   — Замени [Имя] на реальное имя
-   — Для HORECA/ресторанов: добавь упоминание их концепции
-   — Для спортивных организаций: акцентируй бег и инклюзию
-   — Для медиа/PR: предложи совместный контент
-3. ЧТО РАБОТАЕТ В ХОЛОДНЫХ БАЗАХ:
-   — Вариант 3 (вопрос) даёт самый высокий % ответа
-   — Не продавай в первом сообщении
-   — Держи первое сообщение коротким (3-4 предложения)
-   — Не используй шаблонный «Уважаемый» — пиши как человек
-4. УЛУЧШЕНИЕ ПРОЦЕССА:
-   — Разбей на группы по 10-15 контактов и делай паузы (не рассылка, а диалог)
-   — Используй голосовые сообщения для тех, кто уже ответил
-   — Для VIP-контактов (Минуллина Талия, Трукшин Вадим) — сначала изучи публичные интервью
-   — Веди CRM: отметки о статусе каждого контакта</t>
+    <row r="6" ht="250" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>СТРАТЕГИЯ И РЕКОМЕНДАЦИИ</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>ПОРЯДОК КАСАНИЙ:
+  День 1     → TG/VK: Вариант 3 (вопрос без продажи) — лучший % отклика
+  День 3-4   → Email: полный вариант письма
+  День 6-7   → TG/VK: Вариант 2 (деловой) — 1 раз, не надоедать
+  Далее      → Максимум 3 касания. Не преследовать.
+ПЕРСОНАЛИЗАЦИЯ (обязательно!):
+  • Замени [Имя] на реальное имя
+  • В колонках «Сообщение вар. 1-3» уже вставлены персонализированные тексты
+  • Для HoReCa/ресторанов — упомяни их концепцию
+  • Для спорт. организаций — акцент на бег и инклюзию
+  • Для медиа/PR — предложи совместный контент
+ЧТО РАБОТАЕТ С ХОЛОДНОЙ БАЗОЙ:
+  • Вариант 3 (вопрос) — самый высокий % ответа
+  • Первое сообщение: 3-4 предложения, без продажи
+  • Не пиши «Уважаемый» — пиши как человек
+  • Голосовые сообщения дают хороший отклик у тех, кто ответил
+VIP-КОНТАКТЫ (требуют отдельного подхода):
+  • Минуллина Талия — рук. Агентства инвестиций РТ: изучи её интервью перед написанием
+  • Трукшин Вадим — ГК MANTERA: акцент на аудиторию любителей активного отдыха
+  • Суфиянова Евгения — GASTREET/HORECA HUB: она работает в мероприятиях, поймёт язык
+  • Зайченко Иван — «Жизньмарт»: у него TG и TenChat, пиши туда
+ПРИОРИТЕТ КОНТАКТОВ:
+  Уровень A (есть TG + email): строки с заполненными обоими полями → пиши сначала
+  Уровень B (есть TG или email): большинство контактов
+  Уровень C (нет ничего): Овчинников Евгений, Невзорова Ирина — пропустить или уточнить
+КАК УЛУЧШИТЬ ПРОЦЕСС:
+  • Веди статус в таблице (добавь столбец: Написал / Ответил / Созвон / Отказ)
+  • Работай группами по 10-15 контактов, не рассылкой
+  • Отправляй в разное время суток (оптимально: вт-чт, 10:00-12:00 или 15:00-17:00)
+  • Для ресторанов/HoReCa — не пиши в пятницу вечером и выходные</t>
         </is>
       </c>
     </row>
